--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_363_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_363_R37.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0397</v>
+        <v>5.6877</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5588</v>
+        <v>4.3412</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4809</v>
+        <v>1.3465</v>
       </c>
       <c r="G2" t="n">
         <v>5.7846</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.049</v>
+        <v>-0.4011</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.411</v>
+        <v>-0.6286</v>
       </c>
       <c r="U2" t="n">
-        <v>0.362</v>
+        <v>0.2276</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4365</v>
+        <v>1.7919</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6099</v>
+        <v>1.2984</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1734</v>
+        <v>0.4935</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0901</v>
+        <v>1.4813</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0974</v>
+        <v>-1.9316</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0073</v>
+        <v>3.4129</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3603</v>
+        <v>2.0998</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.339</v>
+        <v>-1.1624</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6993</v>
+        <v>3.2622</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4504</v>
+        <v>-0.6185</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7584</v>
+        <v>-0.7692</v>
       </c>
       <c r="O3" t="n">
-        <v>0.308</v>
+        <v>0.1507</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0653</v>
+        <v>-1.0811</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1077</v>
+        <v>-0.9432</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0425</v>
+        <v>-0.1379</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0278</v>
+        <v>1.0951</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5343</v>
+        <v>1.0332</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4935</v>
+        <v>0.0619</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4813</v>
+        <v>-0.0901</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.9316</v>
+        <v>-1.0974</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4129</v>
+        <v>1.0073</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0998</v>
+        <v>0.3603</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1624</v>
+        <v>-0.339</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2622</v>
+        <v>0.6993</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6185</v>
+        <v>-0.4504</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7692</v>
+        <v>-0.7584</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1507</v>
+        <v>0.308</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8452</v>
+        <v>-0.2761</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7073</v>
+        <v>0.5311</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1379</v>
+        <v>-0.8072</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W4" t="n">
         <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1666</v>
+        <v>-0.142</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8172</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6506</v>
+        <v>0.4826</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1985</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1041</v>
+        <v>0.1287</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.55</v>
+        <v>-0.3574</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6541</v>
+        <v>0.4861</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6423</v>
+        <v>-0.4571</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6693</v>
+        <v>0.7873</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3116</v>
+        <v>-1.2444</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0788</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4191</v>
+        <v>-0.2339</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8962</v>
+        <v>-0.7782</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4771</v>
+        <v>0.5443</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2051</v>
+        <v>-0.9452</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9153</v>
+        <v>-0.7226</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2898</v>
+        <v>-0.2226</v>
       </c>
       <c r="G7" t="n">
         <v>-2.129</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3286</v>
+        <v>-0.0688</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2161</v>
+        <v>-0.0235</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V7" t="n">
         <v>0.7886</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4684</v>
+        <v>-1.738</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2792</v>
+        <v>-1.5151</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1892</v>
+        <v>-0.2228</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3041</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5162</v>
+        <v>0.2467</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2526</v>
+        <v>0.219</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2392</v>
+        <v>-1.8853</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.2082</v>
       </c>
       <c r="F9" t="n">
         <v>-1.6772</v>
@@ -1156,10 +1156,10 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7888</v>
+        <v>-1.435</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4936</v>
+        <v>-1.1398</v>
       </c>
       <c r="U9" t="n">
         <v>-0.2952</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1735</v>
+        <v>-2.4247</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9806</v>
+        <v>-2.1982</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1929</v>
+        <v>-0.2265</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1199</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8938</v>
+        <v>-1.145</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2617</v>
+        <v>-0.4793</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6321</v>
+        <v>-0.6657</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6089000000000007</v>
+        <v>0.9824000000000006</v>
       </c>
       <c r="E11" t="n">
-        <v>1.818000000000001</v>
+        <v>2.1915</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.209100000000001</v>
+        <v>-1.209</v>
       </c>
       <c r="G11" t="n">
         <v>1.1993</v>
@@ -1312,13 +1312,13 @@
         <v>13.9171</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.6389</v>
+        <v>-4.2656</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.1646</v>
+        <v>-3.791199999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4744</v>
+        <v>-0.4742000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7501</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7638</v>
+        <v>1.7367</v>
       </c>
       <c r="E12" t="n">
-        <v>4.6269</v>
+        <v>1.1997</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8631</v>
+        <v>0.537</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6935</v>
+        <v>3.0825</v>
       </c>
       <c r="H12" t="n">
-        <v>2.042</v>
+        <v>2.4802</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3485</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6843</v>
+        <v>2.0998</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4535</v>
+        <v>1.9158</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2308</v>
+        <v>0.184</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9908</v>
+        <v>0.9827</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4116</v>
+        <v>0.5644</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5792</v>
+        <v>0.4183</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.9278</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.1598</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-1.3917</v>
       </c>
       <c r="R12" t="n">
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>4.23</v>
+        <v>0.796</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3343</v>
+        <v>0.2596</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.5364</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1514</v>
+        <v>1.6578</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4356</v>
+        <v>2.6217</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7158</v>
+        <v>-0.9639</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0825</v>
+        <v>0.6935</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4802</v>
+        <v>2.042</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6022999999999999</v>
+        <v>-1.3485</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0998</v>
+        <v>2.6843</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9158</v>
+        <v>2.4535</v>
       </c>
       <c r="L13" t="n">
-        <v>0.184</v>
+        <v>0.2308</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9827</v>
+        <v>-1.9908</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5644</v>
+        <v>-0.4116</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4183</v>
+        <v>-1.5792</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R13" t="n">
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2107</v>
+        <v>2.124</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4955</v>
+        <v>1.3291</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3063</v>
+        <v>1.4242</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4565</v>
+        <v>1.5744</v>
       </c>
       <c r="F14" t="n">
         <v>-0.1502</v>
@@ -1546,10 +1546,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9357</v>
+        <v>1.0537</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1889</v>
+        <v>0.3068</v>
       </c>
       <c r="U14" t="n">
         <v>0.7468</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.182</v>
+        <v>1.4186</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4434</v>
+        <v>1.0215</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2614</v>
+        <v>0.3971</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9003</v>
+        <v>0.1098</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3587</v>
+        <v>-1.0276</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2589</v>
+        <v>1.1374</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6487</v>
+        <v>1.5905</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3865</v>
+        <v>0.1855</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2622</v>
+        <v>1.405</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7484</v>
+        <v>-1.4807</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7452</v>
+        <v>-1.2131</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0033</v>
+        <v>-0.2676</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R15" t="n">
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9502</v>
+        <v>0.7185</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0455</v>
+        <v>0.2324</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0953</v>
+        <v>0.4861</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9416</v>
+        <v>1.3875</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8541</v>
+        <v>1.1019</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9124</v>
+        <v>0.2856</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.585</v>
+        <v>1.175</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1478</v>
+        <v>1.5029</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7327</v>
+        <v>-0.328</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9926</v>
+        <v>0.6677</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8822</v>
+        <v>1.1497</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1104</v>
+        <v>-0.482</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5775</v>
+        <v>0.5072</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7344</v>
+        <v>0.3532</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8431</v>
+        <v>0.154</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2415</v>
+        <v>0.8905</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7468</v>
+        <v>0.13</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4946</v>
+        <v>0.7604</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6083</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3184</v>
+        <v>1.3843</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3138</v>
+        <v>1.6793</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0046</v>
+        <v>-0.295</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1098</v>
+        <v>1.9003</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0276</v>
+        <v>-1.3587</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1374</v>
+        <v>3.2589</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5905</v>
+        <v>3.6487</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1855</v>
+        <v>0.3865</v>
       </c>
       <c r="L17" t="n">
-        <v>1.405</v>
+        <v>3.2622</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4807</v>
+        <v>-1.7484</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2131</v>
+        <v>-1.7452</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2676</v>
+        <v>-0.0033</v>
       </c>
       <c r="P17" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-1.1598</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3818</v>
+        <v>-0.7479</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4753</v>
+        <v>-0.8096</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0936</v>
+        <v>0.0617</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1838</v>
+        <v>1.3792</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1583</v>
+        <v>3.09</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3421</v>
+        <v>-1.7108</v>
       </c>
       <c r="G18" t="n">
-        <v>1.175</v>
+        <v>-0.585</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5029</v>
+        <v>0.1478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.328</v>
+        <v>-0.7327</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6677</v>
+        <v>1.9926</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1497</v>
+        <v>1.8822</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.482</v>
+        <v>0.1104</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5072</v>
+        <v>-2.5775</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3532</v>
+        <v>-1.7344</v>
       </c>
       <c r="O18" t="n">
-        <v>0.154</v>
+        <v>-0.8431</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8136</v>
+        <v>-0.5109</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1327</v>
+        <v>-0.293</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5361</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8395</v>
+        <v>-0.5128</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4793</v>
+        <v>-2.0074</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6398</v>
+        <v>1.4946</v>
       </c>
       <c r="G19" t="n">
         <v>0.1982</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9107</v>
+        <v>1.2373</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5149</v>
+        <v>-0.0431</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4255</v>
+        <v>1.2803</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7886</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8425</v>
+        <v>-2.0898</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2504</v>
+        <v>-3.7222</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4079</v>
+        <v>1.6324</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1222</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5992</v>
+        <v>0.3519</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4604</v>
+        <v>-0.0114</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1388</v>
+        <v>0.3633</v>
       </c>
       <c r="V20" t="n">
         <v>0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1774</v>
+        <v>-2.1096</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3181</v>
+        <v>-1.0822</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-1.0274</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8899</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1041</v>
+        <v>0.172</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4775</v>
+        <v>0.3095</v>
       </c>
       <c r="V21" t="n">
         <v>0.5361</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2292</v>
+        <v>-5.4987</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0316</v>
+        <v>-4.2675</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1975</v>
+        <v>-1.2311</v>
       </c>
       <c r="G22" t="n">
         <v>-5.364</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.3666</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0351</v>
+        <v>-0.2711</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0619</v>
+        <v>-0.0955</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6088999999999993</v>
+        <v>0.1773999999999978</v>
       </c>
       <c r="E23" t="n">
-        <v>1.209199999999998</v>
+        <v>1.2092</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.818000000000001</v>
+        <v>-1.0317</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1993</v>
       </c>
       <c r="H23" t="n">
-        <v>3.770099999999999</v>
+        <v>3.7701</v>
       </c>
       <c r="I23" t="n">
         <v>-4.9694</v>
@@ -2233,10 +2233,10 @@
         <v>-11.6729</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.333299999999999</v>
+        <v>-5.3333</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.339700000000001</v>
+        <v>-6.339699999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-5.798799999999999</v>
@@ -2248,13 +2248,13 @@
         <v>8.118599999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>4.6389</v>
+        <v>5.4255</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4744999999999991</v>
+        <v>0.4742999999999998</v>
       </c>
       <c r="U23" t="n">
-        <v>4.1646</v>
+        <v>4.950899999999999</v>
       </c>
       <c r="V23" t="n">
         <v>1.7501</v>
